--- a/data/raw.xlsx
+++ b/data/raw.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WXQ\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\ugt_ml\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB4DF43-7631-4350-9E76-35E21DDAE627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C338DCC1-70E8-4951-90D0-035918102197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{08A2FE0B-1636-49B5-B4C3-F0BD58A361BA}"/>
+    <workbookView xWindow="7245" yWindow="3180" windowWidth="28800" windowHeight="15345" xr2:uid="{08A2FE0B-1636-49B5-B4C3-F0BD58A361BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -171,11 +171,11 @@
     <t>F208M-H93M-V129A-F379A</t>
   </si>
   <si>
-    <t>突变体</t>
+    <t>variant</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>比酶活（mU/mg)</t>
+    <t>activity</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -274,9 +274,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -314,7 +314,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -420,7 +420,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -562,7 +562,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -571,13 +571,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC05E681-46F5-4770-AACB-E8D729A6292B}">
   <dimension ref="A1:B49"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.9140625" customWidth="1"/>
-    <col min="2" max="2" width="15.9140625" customWidth="1"/>
+    <col min="1" max="1" width="25.875" customWidth="1"/>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
@@ -585,7 +585,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -593,7 +593,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -601,7 +601,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -617,7 +617,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -625,7 +625,7 @@
         <v>4.3659999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -633,7 +633,7 @@
         <v>12.135999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -641,7 +641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -657,7 +657,7 @@
         <v>2.4420000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -665,7 +665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -673,7 +673,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -713,7 +713,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -721,7 +721,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -729,7 +729,7 @@
         <v>6.2160000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -737,7 +737,7 @@
         <v>2.738</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -745,7 +745,7 @@
         <v>2.6640000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -753,7 +753,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -761,7 +761,7 @@
         <v>9.4719999999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -769,7 +769,7 @@
         <v>0.222</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -777,7 +777,7 @@
         <v>0.29599999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -785,7 +785,7 @@
         <v>0.29599999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -793,7 +793,7 @@
         <v>1.1839999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
@@ -801,7 +801,7 @@
         <v>3.0339999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -809,7 +809,7 @@
         <v>9.7680000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -817,7 +817,7 @@
         <v>9.7680000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -825,7 +825,7 @@
         <v>7.4740000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -833,7 +833,7 @@
         <v>3.4039999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
@@ -841,7 +841,7 @@
         <v>9.8420000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -849,7 +849,7 @@
         <v>11.766</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -857,7 +857,7 @@
         <v>8.2140000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -865,7 +865,7 @@
         <v>4.6619999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
@@ -873,7 +873,7 @@
         <v>11.618</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -881,7 +881,7 @@
         <v>5.92</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
@@ -889,7 +889,7 @@
         <v>11.544</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
@@ -897,7 +897,7 @@
         <v>9.7680000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
@@ -905,7 +905,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
@@ -913,7 +913,7 @@
         <v>9.0280000000000005</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
@@ -921,7 +921,7 @@
         <v>9.5459999999999994</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
@@ -929,7 +929,7 @@
         <v>7.1040000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
@@ -937,7 +937,7 @@
         <v>10.582000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
@@ -945,7 +945,7 @@
         <v>0.29599999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
@@ -953,7 +953,7 @@
         <v>11.247999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
@@ -961,7 +961,7 @@
         <v>10.507999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
